--- a/data/observations.xlsx
+++ b/data/observations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>auteur</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>categorie</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>categorie</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>highlight</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
@@ -498,25 +488,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr Aubert</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UF Cardiologie</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Clinique</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Dyspnée de repos avec orthopnée</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Dyspnée de repos avec orthopnée à l'admission, crépitants bilatéraux aux bases, œdèmes des membres inférieurs.</t>
         </is>
@@ -545,21 +525,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UF Cardiologie</t>
+          <t>Fonctionnelle</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>Fonctionnelle</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Amélioration nette de la dyspnée, périmètre de marche en progression, plus d'orthopnée.</t>
         </is>
@@ -588,21 +562,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UF Cardiologie</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>Sociale</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
         <is>
           <t>Patiente vivant seule, aide à domicile déjà en place 2x/semaine ; fille disponible pour renfort ponctuel.</t>
         </is>
@@ -631,21 +599,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr Caron</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>Clinique</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
         <is>
           <t>Fièvre à 39.2°C, toux productive, douleur basithoracique droite à l'admission.</t>
         </is>
@@ -674,21 +636,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr Nguyen</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>Fonctionnelle</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>Fonctionnelle</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
         <is>
           <t>Apyrexie depuis 48h, amélioration de la toux, reprise d'une activité normale.</t>
         </is>
@@ -717,25 +673,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr Lefevre</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UF Chirurgie orthopédique</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>Clinique</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Douleur post-opératoire</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>Douleur post-opératoire bien contrôlée, cicatrice propre et sèche, pas de signe inflammatoire.</t>
         </is>

--- a/data/observations.xlsx
+++ b/data/observations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -579,37 +579,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REC-2024-00099</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
+          <t>REC-2024-00187</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>o1</t>
+          <t>hobs1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clinique</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fièvre à 39.2°C, toux productive, douleur basithoracique droite à l'admission.</t>
+          <t>Consultation de suivi ambulatoire, patiente stable, pas de décompensation depuis la dernière hospitalisation.</t>
         </is>
       </c>
     </row>
@@ -621,17 +617,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>o2</t>
+          <t>o1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -641,47 +637,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fonctionnelle</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apyrexie depuis 48h, amélioration de la toux, reprise d'une activité normale.</t>
+          <t>Fièvre à 39.2°C, toux productive, douleur basithoracique droite à l'admission.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>REC-2024-00099</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ID0000201</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>o2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>UF Pneumologie</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fonctionnelle</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Apyrexie depuis 48h, amélioration de la toux, reprise d'une activité normale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>REC-2024-00234</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ID0000156</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>o1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Clinique</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Douleur post-opératoire bien contrôlée, cicatrice propre et sèche, pas de signe inflammatoire.</t>
         </is>
